--- a/NBFC-MF/Borrowers/Kakwa_Lamdaibung_Group_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Kakwa_Lamdaibung_Group_Weekly.xlsx
@@ -1002,31 +1002,33 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="23" t="str">
+      <c r="A9" s="19">
+        <v>46281</v>
+      </c>
+      <c r="B9" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C9" s="20"/>
-      <c r="D9" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E9" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F9" s="21" t="str">
+      <c r="D9" s="21">
+        <f t="shared" si="0"/>
+        <v>4200</v>
+      </c>
+      <c r="E9" s="21">
+        <f t="shared" si="1"/>
+        <v>756.27837430915508</v>
+      </c>
+      <c r="F9" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G9" s="21" t="str">
+        <v>3443.721625690845</v>
+      </c>
+      <c r="G9" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H9" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>34272.959564168894</v>
+      </c>
+      <c r="H9" s="21">
+        <f t="shared" si="2"/>
+        <v>25727.040435831106</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>7</v>
@@ -1130,7 +1132,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1165,7 +1167,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>42000</v>
+        <v>37800</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1200,7 +1202,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>37716.681189859737</v>
+        <v>34272.959564168894</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1235,7 +1237,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>22283.318810140263</v>
+        <v>25727.040435831106</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Kakwa_Lamdaibung_Group_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Kakwa_Lamdaibung_Group_Weekly.xlsx
@@ -1038,31 +1038,33 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="22" t="str">
+      <c r="A10" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B10" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>9</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F10" s="1" t="str">
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
+        <v>4200</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="1"/>
+        <v>687.22637634728358</v>
+      </c>
+      <c r="F10" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G10" s="1" t="str">
+        <v>3512.7736236527162</v>
+      </c>
+      <c r="G10" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H10" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>30760.185940516178</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="2"/>
+        <v>29239.814059483822</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>8</v>
@@ -1132,7 +1134,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1167,7 +1169,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>37800</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1202,7 +1204,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>34272.959564168894</v>
+        <v>30760.185940516178</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1237,7 +1239,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>25727.040435831106</v>
+        <v>29239.814059483822</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Kakwa_Lamdaibung_Group_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Kakwa_Lamdaibung_Group_Weekly.xlsx
@@ -1074,67 +1074,71 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19"/>
-      <c r="B11" s="23" t="str">
+      <c r="A11" s="19">
+        <v>46295</v>
+      </c>
+      <c r="B11" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E11" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F11" s="21" t="str">
+      <c r="D11" s="21">
+        <f t="shared" si="0"/>
+        <v>4200</v>
+      </c>
+      <c r="E11" s="21">
+        <f t="shared" si="1"/>
+        <v>616.78977796156971</v>
+      </c>
+      <c r="F11" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G11" s="21" t="str">
+        <v>3583.2102220384304</v>
+      </c>
+      <c r="G11" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H11" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>27176.975718477748</v>
+      </c>
+      <c r="H11" s="21">
+        <f t="shared" si="2"/>
+        <v>32823.024281522252</v>
       </c>
       <c r="J11" s="14"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="22" t="str">
+      <c r="A12" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B12" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>11</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F12" s="1" t="str">
+      <c r="D12" s="1">
+        <f t="shared" si="0"/>
+        <v>4200</v>
+      </c>
+      <c r="E12" s="1">
+        <f t="shared" si="1"/>
+        <v>544.94081575065979</v>
+      </c>
+      <c r="F12" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G12" s="1" t="str">
+        <v>3655.0591842493404</v>
+      </c>
+      <c r="G12" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H12" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>23521.916534228407</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="2"/>
+        <v>36478.08346577159</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1169,7 +1173,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>33600</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1204,7 +1208,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>30760.185940516178</v>
+        <v>23521.916534228407</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1239,7 +1243,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>29239.814059483822</v>
+        <v>36478.08346577159</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
